--- a/03_Cluster_groups/Muscle_size/Figures/F1_Overview/c_data/f1_overview.xlsx
+++ b/03_Cluster_groups/Muscle_size/Figures/F1_Overview/c_data/f1_overview.xlsx
@@ -800,7 +800,7 @@
     <t>03_Cluster_groups/Muscle_size/03_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
   </si>
   <si>
-    <t>c9f61aab54ce694d0ce15c8b10ce87b0</t>
+    <t>27e79d443001f0e053450f5f5bfba1bb</t>
   </si>
   <si>
     <t>set_tests</t>
@@ -809,7 +809,7 @@
     <t>03_Cluster_groups/Muscle_size/04_Set_Contrasts/c_data/set_tests.rds</t>
   </si>
   <si>
-    <t>68cbbc144c5aef94cf43a5bf08ea5017</t>
+    <t>f9643fbdf7ae8fd212d60bc86e32de0c</t>
   </si>
   <si>
     <t>gene_sets</t>
@@ -818,7 +818,7 @@
     <t>01_Trunk/04_Gene_Sets/c_data/gene_sets.rds</t>
   </si>
   <si>
-    <t>587e179734739b4ba3ccdf9a51c3f6c0</t>
+    <t>bc1bf66e89df936e164c317354990470</t>
   </si>
   <si>
     <t>00_Input/phenotype.csv</t>
@@ -830,7 +830,7 @@
     <t>03_Cluster_groups/Muscle_size/01_Clustering/c_data/clustering.xlsx</t>
   </si>
   <si>
-    <t>aa4ffd2a334d1c2cad2410b7c0b2bc12</t>
+    <t>bba075674e197b350e4874f7c02b2513</t>
   </si>
   <si>
     <t>groups</t>

--- a/03_Cluster_groups/Muscle_size/Figures/F1_Overview/c_data/f1_overview.xlsx
+++ b/03_Cluster_groups/Muscle_size/Figures/F1_Overview/c_data/f1_overview.xlsx
@@ -107,7 +107,7 @@
     <t>arm</t>
   </si>
   <si>
-    <t>Study group of the participant (HR or LR), or the cluster that replaces it in a cluster arc.</t>
+    <t>Study group of the participant (HR or LR), or the cluster that replaces it in a cluster grouping.</t>
   </si>
   <si>
     <t>group</t>
@@ -800,7 +800,7 @@
     <t>03_Cluster_groups/Muscle_size/03_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
   </si>
   <si>
-    <t>27e79d443001f0e053450f5f5bfba1bb</t>
+    <t>8e4f6de34425961bac985b7893a0bdd7</t>
   </si>
   <si>
     <t>set_tests</t>
@@ -815,7 +815,7 @@
     <t>gene_sets</t>
   </si>
   <si>
-    <t>01_Trunk/04_Gene_Sets/c_data/gene_sets.rds</t>
+    <t>01_Processing/04_Gene_Sets/c_data/gene_sets.rds</t>
   </si>
   <si>
     <t>bc1bf66e89df936e164c317354990470</t>
@@ -830,16 +830,16 @@
     <t>03_Cluster_groups/Muscle_size/01_Clustering/c_data/clustering.xlsx</t>
   </si>
   <si>
-    <t>bba075674e197b350e4874f7c02b2513</t>
-  </si>
-  <si>
-    <t>groups</t>
-  </si>
-  <si>
-    <t>03_Cluster_groups/Muscle_size/01_Clustering/c_data/inputs/groups.rds</t>
-  </si>
-  <si>
-    <t>5aaaee7f5bd1ef8f9ba458af70302873</t>
+    <t>cf9248558373b47eb18a8b459d9e7779</t>
+  </si>
+  <si>
+    <t>design</t>
+  </si>
+  <si>
+    <t>03_Cluster_groups/Muscle_size/02_Design_Contrasts/c_data/design.rds</t>
+  </si>
+  <si>
+    <t>c4dd3f50a2d661a4b677d8502617baaf</t>
   </si>
   <si>
     <t>BiocGenerics</t>

--- a/03_Cluster_groups/Muscle_size/Figures/F1_Overview/c_data/f1_overview.xlsx
+++ b/03_Cluster_groups/Muscle_size/Figures/F1_Overview/c_data/f1_overview.xlsx
@@ -800,7 +800,7 @@
     <t>03_Cluster_groups/Muscle_size/03_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
   </si>
   <si>
-    <t>8e4f6de34425961bac985b7893a0bdd7</t>
+    <t>23b313e174688029e3a472d568ce5203</t>
   </si>
   <si>
     <t>set_tests</t>
@@ -830,7 +830,7 @@
     <t>03_Cluster_groups/Muscle_size/01_Clustering/c_data/clustering.xlsx</t>
   </si>
   <si>
-    <t>cf9248558373b47eb18a8b459d9e7779</t>
+    <t>aa4ba35facde0188e4c027d62b0caae8</t>
   </si>
   <si>
     <t>design</t>
